--- a/Result/profitability/1336.xlsx
+++ b/Result/profitability/1336.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.41</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1925</v>
+        <v>0.1625</v>
       </c>
       <c r="N2" t="n">
-        <v>15.135</v>
+        <v>15.11375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1775</v>
+        <v>0.14625</v>
       </c>
       <c r="N3" t="n">
-        <v>14.2475</v>
+        <v>14.30375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>0.175</v>
+        <v>0.16</v>
       </c>
       <c r="N4" t="n">
-        <v>13.98625</v>
+        <v>13.8075</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.15625</v>
+        <v>0.20375</v>
       </c>
       <c r="N5" t="n">
-        <v>13.8825</v>
+        <v>13.77375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1725</v>
+        <v>0.18375</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5325</v>
+        <v>12.865</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05124999999999999</v>
+        <v>0.07750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>11.165</v>
+        <v>11.77</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0375</v>
+        <v>-0.009999999999999995</v>
       </c>
       <c r="N8" t="n">
-        <v>10.2075</v>
+        <v>10.75125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06</v>
+        <v>-0.05999999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>10.02125</v>
@@ -1645,10 +1645,10 @@
         <v>-0.12</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02375</v>
+        <v>-0.02374999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>9.626250000000001</v>
+        <v>9.626249999999999</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.05125</v>
+        <v>-0.05124999999999998</v>
       </c>
       <c r="N11" t="n">
         <v>10.44875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>689</v>
+      </c>
+      <c r="D75" t="n">
+        <v>575</v>
+      </c>
+      <c r="E75" t="n">
+        <v>114</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>35</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>35</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.38125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3548123980424143</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6.333333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.870000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.04977116704805495</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
